--- a/YouTube이슈분석_개인채널_2026-07-01.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-01.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="155">
   <si>
     <t>날짜</t>
   </si>
@@ -141,88 +141,34 @@
     <t>#반도체 #삼전닉스 #HBM · 삼전닉스 ‘4700조 원 메가 프로젝트’, 성사 배경은? · 4700조, 어디에 어떻게 투자되나? · ‘전력-용수-인재’ 인프라 구축, 문제없나…</t>
   </si>
   <si>
-    <t>재테크</t>
-  </si>
-  <si>
-    <t>주식이 문제가 아니다... 지금 난리난 집값 상황</t>
-  </si>
-  <si>
-    <t>재테크읽어주는 파일럿</t>
-  </si>
-  <si>
-    <t>17:39</t>
-  </si>
-  <si>
-    <t>요즘 같은 시대에 누가 책을 읽겠냐만, 이 책을 보고 누군가가 경제적 자유에 대한 용기를 얻기를 바랍니다! 🔥7월 1일 오전 7시 OPEN🔥 신간 "미국주식비법서 입문편, 실전…</t>
-  </si>
-  <si>
-    <t>7월 10일 SK하이닉스 나스닥 상장!! 숨겨진 진짜 의미는?</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>🔥재파가 메가커피 쏩니다!!🔥 바로이집 앱에서 "내 집 등록"을 하시면, 1분 안에 카톡으로 메가커피 쿠폰이 자동발송됩니다. 앱 다운로드는 아래 링크를 누르시면 됩니다.👇  제…</t>
-  </si>
-  <si>
-    <t>(광고❌) 노는 현금, "3분만에" 안전하게 굴리기</t>
-  </si>
-  <si>
-    <t>시골쥐의 도시생활</t>
+    <t>연예</t>
+  </si>
+  <si>
+    <t>소지섭의 인간쓰레기 참교육 ≪김부장≫ 1~2화 몰아보기 🔥 남북한 전체 싸움 1등 찍어버린 코드명 66이 아빠로 평범하게 살고 있었는데, 웬 깡패들이 딸을 건드네?! 다 D졌어..</t>
+  </si>
+  <si>
+    <t>김시선</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>45:05</t>
+  </si>
+  <si>
+    <t>#소지섭 #김부장 #김시선 #액션 #최대훈 #윤경호 #주상욱 #손나은 #김성규 📺 드라마 ≪김부장≫ 1화~2화의 내용입니다. 채널 SBS에서 매주 (금, 토) 오후 09시 50…</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>차가을 - 내 안부</t>
+  </si>
+  <si>
+    <t>차가을ChaGaEul</t>
   </si>
   <si>
     <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>6:30</t>
-  </si>
-  <si>
-    <t>드디어 고금리 시대가 오고 있습니다. 요즘 주식도 많이 떨어져서 줍줍 찬스로 볼 수도 있지만... 주가가 언제까지 떨어질지도 몰라서 지켜보고 싶은 분들도 있을 거예요. 이럴 때…</t>
-  </si>
-  <si>
-    <t>자기계발</t>
-  </si>
-  <si>
-    <t>[지식뉴스] "이런 리더의 절반은 필요 없어집니다" 토큰 사용량 급증하는데, AI생산성은 왜 안 나올까? 40·50대가 직장에서 생존하는 법 (f.신수정 대표) / 교양이를 부탁해</t>
-  </si>
-  <si>
-    <t>교양이를 부탁해</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>25:16</t>
-  </si>
-  <si>
-    <t>00:00 사람을 움직이는 건 동기 부여가 아니다…리더가 찾아야 할 진짜 스위치 03:00 AI를 도입했는데 생산성은 왜 오히려 안 나올까 05:57 AI 시대의 리더는 지시보…</t>
-  </si>
-  <si>
-    <t>연예</t>
-  </si>
-  <si>
-    <t>소지섭의 인간쓰레기 참교육 ≪김부장≫ 1~2화 몰아보기 🔥 남북한 전체 싸움 1등 찍어버린 코드명 66이 아빠로 평범하게 살고 있었는데, 웬 깡패들이 딸을 건드네?! 다 D졌어..</t>
-  </si>
-  <si>
-    <t>김시선</t>
-  </si>
-  <si>
-    <t>45:05</t>
-  </si>
-  <si>
-    <t>#소지섭 #김부장 #김시선 #액션 #최대훈 #윤경호 #주상욱 #손나은 #김성규 📺 드라마 ≪김부장≫ 1화~2화의 내용입니다. 채널 SBS에서 매주 (금, 토) 오후 09시 50…</t>
-  </si>
-  <si>
-    <t>음악</t>
-  </si>
-  <si>
-    <t>차가을 - 내 안부</t>
-  </si>
-  <si>
-    <t>차가을ChaGaEul</t>
   </si>
   <si>
     <t>4:12</t>
@@ -357,31 +303,6 @@
     <t>인스타 :  이메일 : gojaeyoungbusiness@gmail.com 비하인드 : @gojaeyoung_sub</t>
   </si>
   <si>
-    <t>[EN] [밥묵자]부산사는 꼰대 사투리 고치러 온 거제소녀와 신라공주(feat. 리센느 원이, 제나)</t>
-  </si>
-  <si>
-    <t>꼰대희</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>26:39</t>
-  </si>
-  <si>
-    <t>꼰대희가 진행하는 먹방 토크쇼 '밥묵자' 편입니다.
-써브웨이 샐러드를 먹으며 리센느 멤버(원이·제나, 거제소녀·신라공주 컨셉)와 사투리·근황을 주고받는 토크가 중심입니다.
-구수한 사투리 입담과 게스트 케미, 시청자 이벤트(써브웨이 기프트) 안내가 어우러진 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⏱ 타임라인
-· 0:00  거제·신라 컨셉 게스트 인사
-· 4:10  써브웨이 샐러드 시식 토크
-· 8:58  캐릭터·예능 활동 이야기
-· 18:14  '거제 홍보대사' 됐다는 근황
-· 25:21  다음 멤버 예고하며 마무리</t>
-  </si>
-  <si>
     <t>막국수 하나 더 주세요</t>
   </si>
   <si>
@@ -404,6 +325,18 @@
 · 9:46  예약 핑계로 자리 정리하며 마무리</t>
   </si>
   <si>
+    <t>버뮤다 삼각지대 가서 목숨 걸고 삼각김밥 먹고오기ㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>보물섬</t>
+  </si>
+  <si>
+    <t>22:46</t>
+  </si>
+  <si>
+    <t>강민석은 실종되었습니다.. 아룡하세요~~ 허잇!!!!! 저희 셋의 교복인 바이젝(BYSEC) 에서 10일간, 할인 이벤트를 주셨습니다! 의류들은 직접 개발한 탄탄한 원단이라 장…</t>
+  </si>
+  <si>
     <t>일본</t>
   </si>
   <si>
@@ -443,42 +376,6 @@
     <t>☝️ご視聴ありがとうございます！ チャンネル登録・高評価をよろしくお願いします 📣『ニューズウィーク日本版』のメールマガジンが、ニュースレターに生まれ変わりました。毎日の知的な発見の場として、曜日…</t>
   </si>
   <si>
-    <t>まだ投資しない方が安全だと思っていませんか？10年後に差がつく人が見ている確率とリターンを徹底解説します！</t>
-  </si>
-  <si>
-    <t>鳥海翔の騙されない金融学</t>
-  </si>
-  <si>
-    <t>18:42</t>
-  </si>
-  <si>
-    <t>2026.6.1～書籍購入キャンペーンはこちらから  ▼YouTubeでは話せない限定動画「資産を2倍にするロードマップ」▼  公式LINE限定で配信してます。 【鳥海翔の書籍絶賛発売中！】 Am…</t>
-  </si>
-  <si>
-    <t>金利上昇で本当に売るべき資産はどれなのか？S&amp;P500・全世界株式とサテライト投資の違いを解説します！</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>過去とは違う相場が始まります。NASDAQ100の銘柄変更で見えた次の成長分野とは？</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>[コラボ企画] Korea Vlog with Jobu爆語り/モチベーション/ポジティブに生きたい/悩みうちらのギャル旅/</t>
-  </si>
-  <si>
-    <t>BOMI</t>
-  </si>
-  <si>
-    <t>8:25</t>
-  </si>
-  <si>
-    <t>今回は「Korea Vlog with Jobu」 爆語り/モチベーション/ポジティブに生きたい/悩みうちらのギャル旅を皆さんとシェアハピできればなと思っております✨お楽しみに @JobuJobu…</t>
-  </si>
-  <si>
     <t>ATEEZ(에이티즈) - 'BAD' Official MV</t>
   </si>
   <si>
@@ -509,46 +406,46 @@
     <t>IS:SUE</t>
   </si>
   <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
     <t>5:04</t>
   </si>
   <si>
     <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026…</t>
   </si>
   <si>
-    <t>バケモノがわんさかいる惑星で月を探すホラゲー【Emissary Zero】</t>
-  </si>
-  <si>
-    <t>らっだぁ</t>
-  </si>
-  <si>
-    <t>1:19:11</t>
-  </si>
-  <si>
-    <t>ゲームはこちら→ ◆インスタントグランドマザー → ◆twitterフォローはこちら → ◆さぶちゃんねる → ◆LINEスタンプ → ◆LINE着せ替え → ◆初めて見る人向けオススメシリーズ …</t>
-  </si>
-  <si>
-    <t>【神曲】GONと聴く歴代スプラのバトルBGMが名曲揃いで大興奮だったｗｗｗ</t>
-  </si>
-  <si>
-    <t>GON</t>
-  </si>
-  <si>
-    <t>41:26</t>
-  </si>
-  <si>
-    <t>前回⇒ 次回⇒ 高評価・チャンネル登録・ハイプ 是非 ここで配信中！    ⚡初めてGONを知った人におすすめの動画┃ スプラトゥーン：  ホラーゲーム：  単発動画シリーズ：  GONvs視聴者…</t>
-  </si>
-  <si>
-    <t>イラストの中だけで自分に色塗ってかくれんぼするゲームで100%のバレない裏技を使ったら..</t>
-  </si>
-  <si>
-    <t>てるとくん</t>
-  </si>
-  <si>
-    <t>20:09</t>
-  </si>
-  <si>
-    <t>毎日投稿1265日目！ プロイラストレーターてると選手 高評価チャンネル登録よろしくね✨ てるとくんのセカンドチャンネル！✨✨ @terutokun2 ┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈┈…</t>
+    <t>1人で新作リズム天国を先行プレイして俺より壊れてる奴いんの？</t>
+  </si>
+  <si>
+    <t>1:40:35</t>
+  </si>
+  <si>
+    <t>任天堂、俺のリズムについてこれるかい？ リズム天国 ミラクルスターズ 実況 リズム天国 ミラクルスターズ  --------------------------------------------…</t>
+  </si>
+  <si>
+    <t>【ゆっくり実況:Minecraft】剣魔の世界を統べる Ep.51</t>
+  </si>
+  <si>
+    <t>G. Nチャンネル</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>あと2本で先史時代は終わるらしい 前： 次： 再生リスト： [世界観用語]  フランドール・スカーレット：すけ様 ※動画内の人物は東方projectのキャラクター(二次創作)です。  Music：…</t>
+  </si>
+  <si>
+    <t>【Among Us#342】会議の守護者『アドミラル』参戦！投票先を見抜いて人外を特定せよ！！！【ゆっくり実況】</t>
+  </si>
+  <si>
+    <t>めめんともり</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>【Twitter】 【インスタ】 土曜の動画は揺れております 【前回→youtu.be/Xt5PH41I9Nk】 ◆グッズは下記URLで販売中💀  ◆めめ村LINEスタンプ高評販売中！ ストアで『…</t>
   </si>
   <si>
     <t>스포츠</t>
@@ -570,6 +467,9 @@
   </si>
   <si>
     <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
   </si>
   <si>
     <t>9:20</t>
@@ -1004,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1083,16 +983,16 @@
         <v>22</v>
       </c>
       <c r="I2" s="3">
-        <v>1231840</v>
+        <v>1232271</v>
       </c>
       <c r="J2" s="3">
-        <v>20723</v>
+        <v>20722</v>
       </c>
       <c r="K2" s="3">
         <v>2308</v>
       </c>
       <c r="L2" s="3">
-        <v>143647</v>
+        <v>143398</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>23</v>
@@ -1133,16 +1033,16 @@
         <v>30</v>
       </c>
       <c r="I3" s="3">
-        <v>245393</v>
+        <v>245742</v>
       </c>
       <c r="J3" s="3">
-        <v>28936</v>
+        <v>28939</v>
       </c>
       <c r="K3" s="3">
-        <v>2215</v>
+        <v>2219</v>
       </c>
       <c r="L3" s="3">
-        <v>139088</v>
+        <v>138379</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>31</v>
@@ -1183,16 +1083,16 @@
         <v>37</v>
       </c>
       <c r="I4" s="3">
-        <v>203628</v>
+        <v>205230</v>
       </c>
       <c r="J4" s="3">
-        <v>4717</v>
+        <v>4736</v>
       </c>
       <c r="K4" s="3">
-        <v>1551</v>
+        <v>1555</v>
       </c>
       <c r="L4" s="3">
-        <v>85461</v>
+        <v>84906</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>38</v>
@@ -1227,25 +1127,25 @@
         <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="3">
-        <v>195251</v>
+        <v>2709068</v>
       </c>
       <c r="J5" s="3">
-        <v>5932</v>
+        <v>19486</v>
       </c>
       <c r="K5" s="3">
-        <v>766</v>
+        <v>1843</v>
       </c>
       <c r="L5" s="3">
-        <v>75701</v>
+        <v>356032</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>32</v>
@@ -1265,37 +1165,37 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="3">
+        <v>197714</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3346</v>
+      </c>
+      <c r="K6" s="3">
+        <v>663</v>
+      </c>
+      <c r="L6" s="3">
+        <v>29478</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="I6" s="3">
-        <v>207094</v>
-      </c>
-      <c r="J6" s="3">
-        <v>8393</v>
-      </c>
-      <c r="K6" s="3">
-        <v>905</v>
-      </c>
-      <c r="L6" s="3">
-        <v>38051</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>32</v>
@@ -1315,37 +1215,37 @@
         <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I7" s="3">
-        <v>244017</v>
+        <v>1203399</v>
       </c>
       <c r="J7" s="3">
-        <v>6663</v>
+        <v>41686</v>
       </c>
       <c r="K7" s="3">
-        <v>256</v>
+        <v>2902</v>
       </c>
       <c r="L7" s="3">
-        <v>35936</v>
+        <v>267291</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>32</v>
@@ -1365,34 +1265,34 @@
         <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I8" s="3">
-        <v>22014</v>
+        <v>941670</v>
       </c>
       <c r="J8" s="3">
-        <v>338</v>
+        <v>8236</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>714</v>
       </c>
       <c r="L8" s="3">
-        <v>3542</v>
+        <v>135419</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>58</v>
@@ -1415,37 +1315,37 @@
         <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="3">
+        <v>418128</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6929</v>
+      </c>
+      <c r="K9" s="3">
+        <v>314</v>
+      </c>
+      <c r="L9" s="3">
+        <v>98666</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2688142</v>
-      </c>
-      <c r="J9" s="3">
-        <v>19390</v>
-      </c>
-      <c r="K9" s="3">
-        <v>1831</v>
-      </c>
-      <c r="L9" s="3">
-        <v>354822</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>32</v>
@@ -1465,46 +1365,46 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="3">
+        <v>671907</v>
+      </c>
+      <c r="J10" s="3">
+        <v>6334</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2336</v>
+      </c>
+      <c r="L10" s="3">
+        <v>93345</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="3">
-        <v>195962</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3341</v>
-      </c>
-      <c r="K10" s="3">
-        <v>661</v>
-      </c>
-      <c r="L10" s="3">
-        <v>29374</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="N10" s="4" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1515,10 +1415,10 @@
         <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>69</v>
@@ -1527,34 +1427,34 @@
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" s="3">
-        <v>1195392</v>
+        <v>775456</v>
       </c>
       <c r="J11" s="3">
-        <v>41595</v>
+        <v>7062</v>
       </c>
       <c r="K11" s="3">
-        <v>2899</v>
+        <v>1596</v>
       </c>
       <c r="L11" s="3">
-        <v>267310</v>
+        <v>63176</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1565,46 +1465,46 @@
         <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I12" s="3">
-        <v>938552</v>
+        <v>449587</v>
       </c>
       <c r="J12" s="3">
-        <v>8227</v>
+        <v>18549</v>
       </c>
       <c r="K12" s="3">
-        <v>715</v>
+        <v>2156</v>
       </c>
       <c r="L12" s="3">
-        <v>135652</v>
+        <v>41875</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1615,37 +1515,37 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3">
-        <v>414688</v>
+        <v>2823973</v>
       </c>
       <c r="J13" s="3">
-        <v>6897</v>
+        <v>38706</v>
       </c>
       <c r="K13" s="3">
-        <v>312</v>
+        <v>5365</v>
       </c>
       <c r="L13" s="3">
-        <v>98883</v>
+        <v>479698</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>32</v>
@@ -1668,37 +1568,37 @@
         <v>81</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I14" s="3">
-        <v>670918</v>
+        <v>2182156</v>
       </c>
       <c r="J14" s="3">
-        <v>6334</v>
+        <v>21798</v>
       </c>
       <c r="K14" s="3">
-        <v>2334</v>
+        <v>1777</v>
       </c>
       <c r="L14" s="3">
-        <v>93493</v>
+        <v>250038</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>25</v>
@@ -1718,43 +1618,43 @@
         <v>81</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I15" s="3">
-        <v>774813</v>
+        <v>602130</v>
       </c>
       <c r="J15" s="3">
-        <v>7059</v>
+        <v>8563</v>
       </c>
       <c r="K15" s="3">
-        <v>1596</v>
+        <v>980</v>
       </c>
       <c r="L15" s="3">
-        <v>63208</v>
+        <v>122187</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1762,49 +1662,49 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3">
-        <v>449294</v>
+        <v>170814</v>
       </c>
       <c r="J16" s="3">
-        <v>18540</v>
+        <v>3008</v>
       </c>
       <c r="K16" s="3">
-        <v>2155</v>
+        <v>285</v>
       </c>
       <c r="L16" s="3">
-        <v>41875</v>
+        <v>29564</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1812,13 +1712,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>100</v>
@@ -1827,22 +1727,22 @@
         <v>101</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>102</v>
       </c>
       <c r="I17" s="3">
-        <v>2801144</v>
+        <v>37798</v>
       </c>
       <c r="J17" s="3">
-        <v>38586</v>
+        <v>2720</v>
       </c>
       <c r="K17" s="3">
-        <v>5353</v>
+        <v>215</v>
       </c>
       <c r="L17" s="3">
-        <v>478792</v>
+        <v>21067</v>
       </c>
       <c r="M17" s="4" t="s">
         <v>103</v>
@@ -1862,13 +1762,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>104</v>
@@ -1877,34 +1777,34 @@
         <v>105</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="3">
+        <v>29670</v>
+      </c>
+      <c r="J18" s="3">
+        <v>627</v>
+      </c>
+      <c r="K18" s="3">
+        <v>132</v>
+      </c>
+      <c r="L18" s="3">
+        <v>7737</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="3">
-        <v>1464864</v>
-      </c>
-      <c r="J18" s="3">
-        <v>37241</v>
-      </c>
-      <c r="K18" s="3">
-        <v>4883</v>
-      </c>
-      <c r="L18" s="3">
-        <v>273435</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="N18" s="4" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1912,49 +1812,49 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="I19" s="3">
+        <v>13071660</v>
+      </c>
+      <c r="J19" s="3">
+        <v>381239</v>
+      </c>
+      <c r="K19" s="3">
+        <v>25862</v>
+      </c>
+      <c r="L19" s="3">
+        <v>2041756</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="3">
-        <v>2177022</v>
-      </c>
-      <c r="J19" s="3">
-        <v>21776</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1776</v>
-      </c>
-      <c r="L19" s="3">
-        <v>250200</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="N19" s="4" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1962,40 +1862,40 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1321052</v>
+      </c>
+      <c r="J20" s="3">
+        <v>70502</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5029</v>
+      </c>
+      <c r="L20" s="3">
+        <v>291563</v>
+      </c>
+      <c r="M20" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="3">
-        <v>170570</v>
-      </c>
-      <c r="J20" s="3">
-        <v>3006</v>
-      </c>
-      <c r="K20" s="3">
-        <v>285</v>
-      </c>
-      <c r="L20" s="3">
-        <v>29660</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="N20" s="4" t="s">
         <v>32</v>
@@ -2012,40 +1912,40 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="3">
+        <v>338454</v>
+      </c>
+      <c r="J21" s="3">
+        <v>20157</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1559</v>
+      </c>
+      <c r="L21" s="3">
+        <v>74016</v>
+      </c>
+      <c r="M21" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="3">
-        <v>37702</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2717</v>
-      </c>
-      <c r="K21" s="3">
-        <v>215</v>
-      </c>
-      <c r="L21" s="3">
-        <v>21283</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="N21" s="4" t="s">
         <v>32</v>
@@ -2062,40 +1962,40 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I22" s="3">
-        <v>29416</v>
+        <v>349411</v>
       </c>
       <c r="J22" s="3">
-        <v>626</v>
+        <v>23466</v>
       </c>
       <c r="K22" s="3">
-        <v>131</v>
+        <v>2771</v>
       </c>
       <c r="L22" s="3">
-        <v>7735</v>
+        <v>488523</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N22" s="4" t="s">
         <v>32</v>
@@ -2112,40 +2012,40 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I23" s="3">
-        <v>32915</v>
+        <v>67879</v>
       </c>
       <c r="J23" s="3">
-        <v>1257</v>
+        <v>6893</v>
       </c>
       <c r="K23" s="3">
-        <v>70</v>
+        <v>811</v>
       </c>
       <c r="L23" s="3">
-        <v>31141</v>
+        <v>133618</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>32</v>
@@ -2162,37 +2062,37 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>129</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3">
-        <v>127288</v>
+        <v>95137</v>
       </c>
       <c r="J24" s="3">
-        <v>1810</v>
+        <v>6861</v>
       </c>
       <c r="K24" s="3">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="L24" s="3">
-        <v>22967</v>
+        <v>101474</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>131</v>
@@ -2212,40 +2112,40 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>135</v>
       </c>
       <c r="I25" s="3">
-        <v>117756</v>
+        <v>1623064</v>
       </c>
       <c r="J25" s="3">
-        <v>1880</v>
+        <v>16108</v>
       </c>
       <c r="K25" s="3">
-        <v>66</v>
+        <v>1307</v>
       </c>
       <c r="L25" s="3">
-        <v>16167</v>
+        <v>353659</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N25" s="4" t="s">
         <v>32</v>
@@ -2262,40 +2162,40 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I26" s="3">
-        <v>35014</v>
+        <v>303494</v>
       </c>
       <c r="J26" s="3">
-        <v>969</v>
+        <v>3340</v>
       </c>
       <c r="K26" s="3">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="L26" s="3">
-        <v>4783</v>
+        <v>37149</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N26" s="4" t="s">
         <v>32</v>
@@ -2312,49 +2212,49 @@
         <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I27" s="3">
-        <v>13037296</v>
+        <v>122307</v>
       </c>
       <c r="J27" s="3">
-        <v>380640</v>
+        <v>4777</v>
       </c>
       <c r="K27" s="3">
-        <v>25839</v>
+        <v>561</v>
       </c>
       <c r="L27" s="3">
-        <v>2042751</v>
+        <v>24402</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2362,40 +2262,40 @@
         <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3">
-        <v>1312844</v>
+        <v>168014</v>
       </c>
       <c r="J28" s="3">
-        <v>70434</v>
+        <v>2562</v>
       </c>
       <c r="K28" s="3">
-        <v>5025</v>
+        <v>134</v>
       </c>
       <c r="L28" s="3">
-        <v>291457</v>
+        <v>23188</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>32</v>
@@ -2412,40 +2312,40 @@
         <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D29" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3">
-        <v>336023</v>
+        <v>3254402</v>
       </c>
       <c r="J29" s="3">
-        <v>20067</v>
+        <v>53418</v>
       </c>
       <c r="K29" s="3">
-        <v>1554</v>
+        <v>4008</v>
       </c>
       <c r="L29" s="3">
-        <v>73794</v>
+        <v>520149</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>32</v>
@@ -2454,406 +2354,6 @@
         <v>25</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="3">
-        <v>276339</v>
-      </c>
-      <c r="J30" s="3">
-        <v>9291</v>
-      </c>
-      <c r="K30" s="3">
-        <v>286</v>
-      </c>
-      <c r="L30" s="3">
-        <v>92148</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" s="3">
-        <v>138474</v>
-      </c>
-      <c r="J31" s="3">
-        <v>4920</v>
-      </c>
-      <c r="K31" s="3">
-        <v>544</v>
-      </c>
-      <c r="L31" s="3">
-        <v>90518</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="2">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I32" s="3">
-        <v>79563</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3548</v>
-      </c>
-      <c r="K32" s="3">
-        <v>2214</v>
-      </c>
-      <c r="L32" s="3">
-        <v>68878</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1619177</v>
-      </c>
-      <c r="J33" s="3">
-        <v>16106</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1306</v>
-      </c>
-      <c r="L33" s="3">
-        <v>356450</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I34" s="3">
-        <v>302177</v>
-      </c>
-      <c r="J34" s="3">
-        <v>3332</v>
-      </c>
-      <c r="K34" s="3">
-        <v>31</v>
-      </c>
-      <c r="L34" s="3">
-        <v>37125</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="2">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I35" s="3">
-        <v>122238</v>
-      </c>
-      <c r="J35" s="3">
-        <v>4776</v>
-      </c>
-      <c r="K35" s="3">
-        <v>561</v>
-      </c>
-      <c r="L35" s="3">
-        <v>24459</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="I36" s="3">
-        <v>166900</v>
-      </c>
-      <c r="J36" s="3">
-        <v>2554</v>
-      </c>
-      <c r="K36" s="3">
-        <v>134</v>
-      </c>
-      <c r="L36" s="3">
-        <v>23138</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="2">
-        <v>1</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I37" s="3">
-        <v>3243180</v>
-      </c>
-      <c r="J37" s="3">
-        <v>53315</v>
-      </c>
-      <c r="K37" s="3">
-        <v>4007</v>
-      </c>
-      <c r="L37" s="3">
-        <v>520792</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P37" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2887,14 +2387,6 @@
     <hyperlink ref="O27" r:id="rId26"/>
     <hyperlink ref="O28" r:id="rId27"/>
     <hyperlink ref="O29" r:id="rId28"/>
-    <hyperlink ref="O30" r:id="rId29"/>
-    <hyperlink ref="O31" r:id="rId30"/>
-    <hyperlink ref="O32" r:id="rId31"/>
-    <hyperlink ref="O33" r:id="rId32"/>
-    <hyperlink ref="O34" r:id="rId33"/>
-    <hyperlink ref="O35" r:id="rId34"/>
-    <hyperlink ref="O36" r:id="rId35"/>
-    <hyperlink ref="O37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/YouTube이슈분석_개인채널_2026-07-01.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-01.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="155">
   <si>
     <t>날짜</t>
   </si>
@@ -63,13 +63,475 @@
   </si>
   <si>
     <t>분석방식</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>경제</t>
+  </si>
+  <si>
+    <t>이재용의 저주가 중앙그룹의 돈 줄을 틀어막았다 삼성의 뒤통수를 친 중앙일보의 최후</t>
+  </si>
+  <si>
+    <t>귀에쏙쏙경제학</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>24:51</t>
+  </si>
+  <si>
+    <t>2026년 6월 JTBC의 206억 원 채무불이행과 중앙그룹 핵심 계열사 5곳 법정관리 신청 사태를 해설하는 경제 콘텐츠입니다.
+삼성과 중앙(홍석현 일가)의 혈연 동맹과 그 균열, 7,000억대 스포츠 중계권 도박, 중국 텐센트 자본 유치, 개인투자자 8,000억 피해까지의 흐름을 짚습니다.
+미디어 기업이 무너진 자본 구조와 배경을 하나의 서사로 정리해 줍니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:00  '미디어 역사상 충격적 몰락' 도입
+· 5:04  삼성-중앙의 혈연(외삼촌) 관계 설명
+· 9:34  국정농단 보도와 삼성과의 균열
+· 16:45  올림픽·월드컵 중계권 도박과 투자 유치
+· 23:48  개인투자자 피해로 끝난 청구서 — 결론</t>
+  </si>
+  <si>
+    <t>▶</t>
+  </si>
+  <si>
+    <t>/watch 자막·메타 분석</t>
+  </si>
+  <si>
+    <t>“네가 뭔데 반도체 호남에 주라마라냐?”...자기 탄핵 청원에 더 불붙인 이재명 / 박상규 시사평론가 [굿모닝 대한민국]</t>
+  </si>
+  <si>
+    <t>펜앤마이크TV</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>57:04</t>
+  </si>
+  <si>
+    <t>침묵하지 않는 청년들의 목소리 (나는 보수다) 상금 1,000만원의 주인공은? 참가 신청은 펜앤마이크 인터넷신문 (www.pennmike.com) 에서 가능합니다. 펜앤마이크는…</t>
+  </si>
+  <si>
+    <t>자동 요약(미검수) — 원본 영상으로 내용을 확인하세요.</t>
+  </si>
+  <si>
+    <t>메타데이터+자막(자동)</t>
+  </si>
+  <si>
+    <t>호남 반도체 프로젝트 삼전닉스 투자, 인프라까지 완벽정리!</t>
+  </si>
+  <si>
+    <t>장르만 여의도</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>59:53</t>
+  </si>
+  <si>
+    <t>#반도체 #삼전닉스 #HBM · 삼전닉스 ‘4700조 원 메가 프로젝트’, 성사 배경은? · 4700조, 어디에 어떻게 투자되나? · ‘전력-용수-인재’ 인프라 구축, 문제없나…</t>
+  </si>
+  <si>
+    <t>연예</t>
+  </si>
+  <si>
+    <t>소지섭의 인간쓰레기 참교육 ≪김부장≫ 1~2화 몰아보기 🔥 남북한 전체 싸움 1등 찍어버린 코드명 66이 아빠로 평범하게 살고 있었는데, 웬 깡패들이 딸을 건드네?! 다 D졌어..</t>
+  </si>
+  <si>
+    <t>김시선</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>45:05</t>
+  </si>
+  <si>
+    <t>#소지섭 #김부장 #김시선 #액션 #최대훈 #윤경호 #주상욱 #손나은 #김성규 📺 드라마 ≪김부장≫ 1화~2화의 내용입니다. 채널 SBS에서 매주 (금, 토) 오후 09시 50…</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>차가을 - 내 안부</t>
+  </si>
+  <si>
+    <t>차가을ChaGaEul</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>4:12</t>
+  </si>
+  <si>
+    <t>게임</t>
+  </si>
+  <si>
+    <t>메챠 카멜레온, 혜안져스끼리 해봤는뎈ㅋㅋㅋㅋㅋㅋ🤣</t>
+  </si>
+  <si>
+    <t>혜안</t>
+  </si>
+  <si>
+    <t>36:03</t>
+  </si>
+  <si>
+    <t>꼭꼭 숨꼭져스 [업로드] 금,토,일,월 [문의메일] zxcv34276@gmail.com [인스타그램] @hxxax_ #혜안 #메챠카멜레온 Music provided by 브금대…</t>
+  </si>
+  <si>
+    <t>저는 저를 숨겼습니다</t>
+  </si>
+  <si>
+    <t>랄로</t>
+  </si>
+  <si>
+    <t>47:24</t>
+  </si>
+  <si>
+    <t>랄로 풀코스 youtube.com/@랄롱 치지직 생방송  각종 비지니스 aba060847@gmail.com</t>
+  </si>
+  <si>
+    <t>그림 숨바꼭질 창의력이 넘치기 시작한 유저들</t>
+  </si>
+  <si>
+    <t>우주하마</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>멧차 카멜레온 Meccha Chameleon 우주하마 UZUHAMA</t>
+  </si>
+  <si>
+    <t>IT·테크</t>
+  </si>
+  <si>
+    <t>긴급속보 | 애플, 최소 20만원 넘게 가격 올려버렸다? 갑자기 이런 미친 결정을 한 진짜 이유</t>
+  </si>
+  <si>
+    <t>ITSub잇섭</t>
+  </si>
+  <si>
+    <t>12:18</t>
+  </si>
+  <si>
+    <t>2026년 6월 25일 애플이 대부분 제품 가격을 5.7~54.3% 인상한 속보를 다루는 IT 분석입니다.
+진짜 원인은 AI 데이터센터발 메모리(HBM·D램) 가격 폭등으로, 삼성·하이닉스 등 반도체사의 적자에서 흑자 반전, 챗GPT 등 AI 수요가 메모리 공급의 상당분을 흡수한 구조를 쉽게 설명합니다.
+어떤 제품이 얼마나 올랐고 왜 그런지를 정리해 줍니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:12  오프닝 — 청천벽력 가격 인상 소식
+· 1:37  제품별 인상폭 정리
+· 4:40  인상 이유 — AI발 메모리 가격 폭등
+· 7:01  반도체사 적자→흑자 반전과 공급 쟁탈
+· 10:16  오늘의 결론 — 구매 팁</t>
+  </si>
+  <si>
+    <t>AI 안경 끼고 수능 문제 풀어봤습니다. 그런데 점수가..</t>
+  </si>
+  <si>
+    <t>테크몽 Techmong</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>로키드 AI 글래스를 끼고 수능 모의고사(미적분 포함)를 직접 풀어보는 검증 콘텐츠입니다.
+AI가 시야의 문제를 읽고 답을 알려줘 1등급 수준 점수가 나오는 과정을 보여주고, 시험 보안에 얼마나 위협이 되는지 보안 전문가와 함께 점검합니다.
+AI 안경 구분법·탐지기 테스트·해외 사례까지 다뤄 기술적·제도적 대비를 고민하게 합니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:00  '이게 진짜 된다고?' 도입
+· 0:49  여러 AI 안경 중 로키드를 고른 이유
+· 2:14  모의고사 풀이 — 1등급 수준 점수
+· 7:15  AI 안경 기본 구분법·탐지기 테스트
+· 12:04  '이런 것도 된다고?' 추가 위험 시연</t>
+  </si>
+  <si>
+    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
+  </si>
+  <si>
+    <t>시니어정보 양쌤</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>갤럭시 스마트폰에서 개인정보 보호와 배터리 절약을 동시에 잡는 설정법을 시니어 눈높이로 알려주는 영상입니다.
+플레이스토어 맞춤설정·위치 정보·플레이 프로텍트, 진단 데이터 자동 전송, 안드로이드 맞춤형 서비스 끄기 등을 실제 화면을 따라가며 천천히 설명합니다.
+따라 하기 쉬운 단계별 구성이라 처음 쓰는 분도 바로 적용할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:00  도입 — '지금도 폰이 정보를 보낸다'
+· 0:35  플레이스토어 맞춤설정·위치 끄기
+· 4:36  플레이 프로텍트 데이터 전송 차단
+· 7:36  진단 데이터 자동 전송 끄기
+· 8:31  앱 배터리 최적화 설정</t>
+  </si>
+  <si>
+    <t>라이프</t>
+  </si>
+  <si>
+    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
+  </si>
+  <si>
+    <t>고재영</t>
+  </si>
+  <si>
+    <t>45:14</t>
+  </si>
+  <si>
+    <t>인스타 :  이메일 : gojaeyoungbusiness@gmail.com 비하인드 : @gojaeyoung_sub</t>
+  </si>
+  <si>
+    <t>막국수 하나 더 주세요</t>
+  </si>
+  <si>
+    <t>숏박스</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>숏박스의 스케치 코미디로, 회사 부장과 직원들이 족발집에서 벌이는 상황극입니다.
+보청기 오해, 셀프바, 막국수 추가 주문 같은 일상 디테일을 과장해 웃음을 만듭니다.
+현실 직장·식당 풍경에 공감하게 만드는 숏박스 특유의 디테일 연기가 강점입니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:00  족발집 도착, 자리 잡기
+· 1:28  '우리 회사에 이런 일이' 사건 언급
+· 4:05  족발 등장, 부장 오지랖 개그
+· 7:33  셀프바·부추 리필 개그
+· 9:46  예약 핑계로 자리 정리하며 마무리</t>
+  </si>
+  <si>
+    <t>버뮤다 삼각지대 가서 목숨 걸고 삼각김밥 먹고오기ㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+  </si>
+  <si>
+    <t>보물섬</t>
+  </si>
+  <si>
+    <t>22:46</t>
+  </si>
+  <si>
+    <t>강민석은 실종되었습니다.. 아룡하세요~~ 허잇!!!!! 저희 셋의 교복인 바이젝(BYSEC) 에서 10일간, 할인 이벤트를 주셨습니다! 의류들은 직접 개발한 탄탄한 원단이라 장…</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
+  </si>
+  <si>
+    <t>選挙ドットコムちゃんねる</t>
+  </si>
+  <si>
+    <t>1:03:15</t>
+  </si>
+  <si>
+    <t>【ポスト田﨑史郎氏は今野忍記者！？／PRのプロに聞く！日本のメディア、どうすれば生き残れますか？？】 今回はPR戦略コンサルタントの下矢一良さんにインタビューを行いました！ 政治記者の今野忍さんを…</t>
+  </si>
+  <si>
+    <t>ウクライナの攻勢でGDP下げ ピンチのロシアはよく喋る　後半は日中情報戦本格開戦、戦いの時</t>
+  </si>
+  <si>
+    <t>とっさんTV</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>・ルカシェンコ劇場極み ・カザフスタンからも拒否されらロシア ・米国にSOS ・ウクライナの攻撃でGDP下げ 【日中】 ・中国の対日情報戦が大幅強化</t>
+  </si>
+  <si>
+    <t>【日銀”弱腰利上げ”で続く副作用】市場の攻撃が為替に向かう可能性／植田総裁“病欠”に見る危険な兆候／暮らしへの影響「マイナス面大きい」／有事の円買いは消滅／日本人の資産防衛、最適解は？／加谷珪一の解説</t>
+  </si>
+  <si>
+    <t>ニューズウィーク日本版</t>
+  </si>
+  <si>
+    <t>31:15</t>
+  </si>
+  <si>
+    <t>☝️ご視聴ありがとうございます！ チャンネル登録・高評価をよろしくお願いします 📣『ニューズウィーク日本版』のメールマガジンが、ニュースレターに生まれ変わりました。毎日の知的な発見の場として、曜日…</t>
+  </si>
+  <si>
+    <t>ATEEZ(에이티즈) - 'BAD' Official MV</t>
+  </si>
+  <si>
+    <t>KQ ENTERTAINMENT</t>
+  </si>
+  <si>
+    <t>3:45</t>
+  </si>
+  <si>
+    <t>ATEEZ(에이티즈) - GOLDEN HOUR : Part.5 Spotify ▶  Apple Music ▶  Melon ▶  genie ▶  FLO ▶  본 영상은 전문가 대동…</t>
+  </si>
+  <si>
+    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
+  </si>
+  <si>
+    <t>キヨ。</t>
+  </si>
+  <si>
+    <t>3:49</t>
+  </si>
+  <si>
+    <t>一瞬は永遠の宝物 「瞬間ジャーニー」 Music Video／TOP4(キヨ・レトルト・牛沢・ガッチマン) 作詞：HIROKI(ORANGE RANGE) 作曲：NAOTO(ORANGE RANG…</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
+  </si>
+  <si>
+    <t>IS:SUE</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>5:04</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026…</t>
+  </si>
+  <si>
+    <t>1人で新作リズム天国を先行プレイして俺より壊れてる奴いんの？</t>
+  </si>
+  <si>
+    <t>1:40:35</t>
+  </si>
+  <si>
+    <t>任天堂、俺のリズムについてこれるかい？ リズム天国 ミラクルスターズ 実況 リズム天国 ミラクルスターズ  --------------------------------------------…</t>
+  </si>
+  <si>
+    <t>【ゆっくり実況:Minecraft】剣魔の世界を統べる Ep.51</t>
+  </si>
+  <si>
+    <t>G. Nチャンネル</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>あと2本で先史時代は終わるらしい 前： 次： 再生リスト： [世界観用語]  フランドール・スカーレット：すけ様 ※動画内の人物は東方projectのキャラクター(二次創作)です。  Music：…</t>
+  </si>
+  <si>
+    <t>【Among Us#342】会議の守護者『アドミラル』参戦！投票先を見抜いて人外を特定せよ！！！【ゆっくり実況】</t>
+  </si>
+  <si>
+    <t>めめんともり</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>【Twitter】 【インスタ】 土曜の動画は揺れております 【前回→youtu.be/Xt5PH41I9Nk】 ◆グッズは下記URLで販売中💀  ◆めめ村LINEスタンプ高評販売中！ ストアで『…</t>
+  </si>
+  <si>
+    <t>스포츠</t>
+  </si>
+  <si>
+    <t>【大谷翔平 6試合ぶり第18号3ラン！打った瞬間の“確信歩かない”からの“左手サッと”バットフリップ】ドジャースvsアスレチックス MLB2026シーズン 6.30</t>
+  </si>
+  <si>
+    <t>SPOTVNOW</t>
+  </si>
+  <si>
+    <t>4:07</t>
+  </si>
+  <si>
+    <t>SPOTV NOW 無料登録でハイライト見放題！👉  今年もMLBの試合を日本人選手所属球団を中心にライブ配信いたします！ 無料登録で試合ハイライト・ダイジェスト・インタビューなどのコンテンツを視…</t>
+  </si>
+  <si>
+    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
+  </si>
+  <si>
+    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>今回は、6月はじめにGoogleから届いた謎のメールについて解説します。 動画前半では今回の変更点について、また後半では設定を見直すべきポイントについても解説しますので、是非最後までチェックしてみ…</t>
+  </si>
+  <si>
+    <t>【検証】新型「REDMAGIC 11”S” Pro」を購入。”怪しい動作”どうなった？</t>
+  </si>
+  <si>
+    <t>さいちょう2nd</t>
+  </si>
+  <si>
+    <t>9:53</t>
+  </si>
+  <si>
+    <t>신형 게이밍폰 'REDMAGIC 11S Pro'를 검증하는 콘텐츠입니다.
+이전 모델에서 의심받던 '벤치마크 부스팅'(벤치마크 앱을 인식하면 성능을 비정상적으로 끌어올리는 동작)이 개선됐는지 3DMark 등으로 테스트하고, 발열과 강제 종료(스로틀링)를 확인합니다.
+AI 합성음성으로 진행하는 아마추어 검증이지만 구매 판단에 참고할 만합니다.</t>
+  </si>
+  <si>
+    <t>⏱ 타임라인
+· 0:00  서브 채널 검증 도입
+· 1:04  REDMAGIC 11S Pro 사양 소개
+· 2:30  3DMark 등 벤치마크 테스트
+· 5:59  발열로 강제 종료되는 동작 확인
+· 8:10  배터리 결과·총평으로 마무리</t>
+  </si>
+  <si>
+    <t>【ルームツアー?】自宅にクソでかサーバーを作ったYouTuberがいるらしいので調査してきました。</t>
+  </si>
+  <si>
+    <t>TECH WORLD</t>
+  </si>
+  <si>
+    <t>25:48</t>
+  </si>
+  <si>
+    <t>うんちゃまさんのチャンネル @unchama 今回はうんちゃまさんの自宅サーバーにお邪魔しました。「そういえばおれ自宅にサーバー置いてないかも」という方に是非見ていただきたいです。 【チャンネルス…</t>
+  </si>
+  <si>
+    <t>【2部屋紹介】ヒカキン新居ルームツアー2026【8年ぶりの引っ越し】</t>
+  </si>
+  <si>
+    <t>HikakinTV</t>
+  </si>
+  <si>
+    <t>1:28:58</t>
+  </si>
+  <si>
+    <t>大切な家族のために引っ越すことを決めました。 たくさんの思い出を胸に、新しい場所でまた一歩踏み出します。 これからも、変わらず応援よろしくお願いします。 ◆チャンネル登録はこちら↓  ◆X  ◆イ…</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +543,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,10 +596,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -479,7 +957,1437 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1232271</v>
+      </c>
+      <c r="J2" s="3">
+        <v>20722</v>
+      </c>
+      <c r="K2" s="3">
+        <v>2308</v>
+      </c>
+      <c r="L2" s="3">
+        <v>143398</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <v>245742</v>
+      </c>
+      <c r="J3" s="3">
+        <v>28939</v>
+      </c>
+      <c r="K3" s="3">
+        <v>2219</v>
+      </c>
+      <c r="L3" s="3">
+        <v>138379</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="3">
+        <v>205230</v>
+      </c>
+      <c r="J4" s="3">
+        <v>4736</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1555</v>
+      </c>
+      <c r="L4" s="3">
+        <v>84906</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2709068</v>
+      </c>
+      <c r="J5" s="3">
+        <v>19486</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1843</v>
+      </c>
+      <c r="L5" s="3">
+        <v>356032</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="3">
+        <v>197714</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3346</v>
+      </c>
+      <c r="K6" s="3">
+        <v>663</v>
+      </c>
+      <c r="L6" s="3">
+        <v>29478</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1203399</v>
+      </c>
+      <c r="J7" s="3">
+        <v>41686</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2902</v>
+      </c>
+      <c r="L7" s="3">
+        <v>267291</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="3">
+        <v>941670</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8236</v>
+      </c>
+      <c r="K8" s="3">
+        <v>714</v>
+      </c>
+      <c r="L8" s="3">
+        <v>135419</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="3">
+        <v>418128</v>
+      </c>
+      <c r="J9" s="3">
+        <v>6929</v>
+      </c>
+      <c r="K9" s="3">
+        <v>314</v>
+      </c>
+      <c r="L9" s="3">
+        <v>98666</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="3">
+        <v>671907</v>
+      </c>
+      <c r="J10" s="3">
+        <v>6334</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2336</v>
+      </c>
+      <c r="L10" s="3">
+        <v>93345</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="3">
+        <v>775456</v>
+      </c>
+      <c r="J11" s="3">
+        <v>7062</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1596</v>
+      </c>
+      <c r="L11" s="3">
+        <v>63176</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="3">
+        <v>449587</v>
+      </c>
+      <c r="J12" s="3">
+        <v>18549</v>
+      </c>
+      <c r="K12" s="3">
+        <v>2156</v>
+      </c>
+      <c r="L12" s="3">
+        <v>41875</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2823973</v>
+      </c>
+      <c r="J13" s="3">
+        <v>38706</v>
+      </c>
+      <c r="K13" s="3">
+        <v>5365</v>
+      </c>
+      <c r="L13" s="3">
+        <v>479698</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2182156</v>
+      </c>
+      <c r="J14" s="3">
+        <v>21798</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1777</v>
+      </c>
+      <c r="L14" s="3">
+        <v>250038</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="3">
+        <v>602130</v>
+      </c>
+      <c r="J15" s="3">
+        <v>8563</v>
+      </c>
+      <c r="K15" s="3">
+        <v>980</v>
+      </c>
+      <c r="L15" s="3">
+        <v>122187</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="3">
+        <v>170814</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3008</v>
+      </c>
+      <c r="K16" s="3">
+        <v>285</v>
+      </c>
+      <c r="L16" s="3">
+        <v>29564</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="3">
+        <v>37798</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2720</v>
+      </c>
+      <c r="K17" s="3">
+        <v>215</v>
+      </c>
+      <c r="L17" s="3">
+        <v>21067</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" s="3">
+        <v>29670</v>
+      </c>
+      <c r="J18" s="3">
+        <v>627</v>
+      </c>
+      <c r="K18" s="3">
+        <v>132</v>
+      </c>
+      <c r="L18" s="3">
+        <v>7737</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="3">
+        <v>13071660</v>
+      </c>
+      <c r="J19" s="3">
+        <v>381239</v>
+      </c>
+      <c r="K19" s="3">
+        <v>25862</v>
+      </c>
+      <c r="L19" s="3">
+        <v>2041756</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1321052</v>
+      </c>
+      <c r="J20" s="3">
+        <v>70502</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5029</v>
+      </c>
+      <c r="L20" s="3">
+        <v>291563</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="3">
+        <v>338454</v>
+      </c>
+      <c r="J21" s="3">
+        <v>20157</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1559</v>
+      </c>
+      <c r="L21" s="3">
+        <v>74016</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="3">
+        <v>349411</v>
+      </c>
+      <c r="J22" s="3">
+        <v>23466</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2771</v>
+      </c>
+      <c r="L22" s="3">
+        <v>488523</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="3">
+        <v>67879</v>
+      </c>
+      <c r="J23" s="3">
+        <v>6893</v>
+      </c>
+      <c r="K23" s="3">
+        <v>811</v>
+      </c>
+      <c r="L23" s="3">
+        <v>133618</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="3">
+        <v>95137</v>
+      </c>
+      <c r="J24" s="3">
+        <v>6861</v>
+      </c>
+      <c r="K24" s="3">
+        <v>269</v>
+      </c>
+      <c r="L24" s="3">
+        <v>101474</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1623064</v>
+      </c>
+      <c r="J25" s="3">
+        <v>16108</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1307</v>
+      </c>
+      <c r="L25" s="3">
+        <v>353659</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="3">
+        <v>303494</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3340</v>
+      </c>
+      <c r="K26" s="3">
+        <v>31</v>
+      </c>
+      <c r="L26" s="3">
+        <v>37149</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I27" s="3">
+        <v>122307</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4777</v>
+      </c>
+      <c r="K27" s="3">
+        <v>561</v>
+      </c>
+      <c r="L27" s="3">
+        <v>24402</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" s="3">
+        <v>168014</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2562</v>
+      </c>
+      <c r="K28" s="3">
+        <v>134</v>
+      </c>
+      <c r="L28" s="3">
+        <v>23188</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I29" s="3">
+        <v>3254402</v>
+      </c>
+      <c r="J29" s="3">
+        <v>53418</v>
+      </c>
+      <c r="K29" s="3">
+        <v>4008</v>
+      </c>
+      <c r="L29" s="3">
+        <v>520149</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="O3" r:id="rId2"/>
+    <hyperlink ref="O4" r:id="rId3"/>
+    <hyperlink ref="O5" r:id="rId4"/>
+    <hyperlink ref="O6" r:id="rId5"/>
+    <hyperlink ref="O7" r:id="rId6"/>
+    <hyperlink ref="O8" r:id="rId7"/>
+    <hyperlink ref="O9" r:id="rId8"/>
+    <hyperlink ref="O10" r:id="rId9"/>
+    <hyperlink ref="O11" r:id="rId10"/>
+    <hyperlink ref="O12" r:id="rId11"/>
+    <hyperlink ref="O13" r:id="rId12"/>
+    <hyperlink ref="O14" r:id="rId13"/>
+    <hyperlink ref="O15" r:id="rId14"/>
+    <hyperlink ref="O16" r:id="rId15"/>
+    <hyperlink ref="O17" r:id="rId16"/>
+    <hyperlink ref="O18" r:id="rId17"/>
+    <hyperlink ref="O19" r:id="rId18"/>
+    <hyperlink ref="O20" r:id="rId19"/>
+    <hyperlink ref="O21" r:id="rId20"/>
+    <hyperlink ref="O22" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O25" r:id="rId24"/>
+    <hyperlink ref="O26" r:id="rId25"/>
+    <hyperlink ref="O27" r:id="rId26"/>
+    <hyperlink ref="O28" r:id="rId27"/>
+    <hyperlink ref="O29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
